--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -10262,7 +10262,7 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026 07:57 PM IST</t>
+          <t>14/09/2026 09:52 PM IST</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>11/09/2026 07:57 PM IST</t>
+          <t>14/09/2026 09:52 PM IST</t>
         </is>
       </c>
     </row>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T131"/>
+  <dimension ref="A1:T132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10494,6 +10494,82 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>17/09/2026 08:31 PM IST</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>191.7200012207031</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>4924218 / 1889379 (2.6x)</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>192.9</v>
+      </c>
+      <c r="H132" s="4" t="n">
+        <v>193.6</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>188.6</v>
+      </c>
+      <c r="J132" s="6" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="K132" s="7" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="L132" s="8" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="M132" s="7" t="n">
+        <v>208.7</v>
+      </c>
+      <c r="N132" s="8" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="O132" s="4" t="n">
+        <v>188.8399963378906</v>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="n">
+        <v>193.6</v>
+      </c>
+      <c r="R132" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.191.7 above EMA200 Rs.181.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 192.9</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>17/09/2026 08:31 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T132"/>
+  <dimension ref="A1:T137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10570,6 +10570,386 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 08:02 PM IST</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>JSWINFRA</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>348.25</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>25470641 / 2234928 (11.4x)</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>357</v>
+      </c>
+      <c r="H133" s="4" t="n">
+        <v>360.2</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="K133" s="7" t="n">
+        <v>403.7</v>
+      </c>
+      <c r="L133" s="8" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M133" s="7" t="n">
+        <v>425.5</v>
+      </c>
+      <c r="N133" s="8" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="O133" s="4" t="n">
+        <v>326.6499938964844</v>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="n">
+        <v>360.2</v>
+      </c>
+      <c r="R133" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.348.2 above EMA200 Rs.304.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 60 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 11.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 11.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 357.0</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 08:02 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 08:02 PM IST</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>479.5499877929688</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>1065010 / 815416 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="n">
+        <v>481.5</v>
+      </c>
+      <c r="H134" s="4" t="n">
+        <v>486.3</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>452.4</v>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="K134" s="7" t="n">
+        <v>554.2</v>
+      </c>
+      <c r="L134" s="8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M134" s="7" t="n">
+        <v>588.1</v>
+      </c>
+      <c r="N134" s="8" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="O134" s="4" t="n">
+        <v>469.2999877929688</v>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="n">
+        <v>486.3</v>
+      </c>
+      <c r="R134" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.479.5 above EMA200 Rs.388.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 54 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 481.5</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 08:02 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 08:02 PM IST</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>1734</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>1209478 / 739012 (1.6x)</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="n">
+        <v>1734</v>
+      </c>
+      <c r="H135" s="4" t="n">
+        <v>1746.9</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>1660.7</v>
+      </c>
+      <c r="J135" s="6" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="K135" s="7" t="n">
+        <v>1919.4</v>
+      </c>
+      <c r="L135" s="8" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="M135" s="7" t="n">
+        <v>2005.6</v>
+      </c>
+      <c r="N135" s="8" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="O135" s="4" t="n">
+        <v>1643</v>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="n">
+        <v>1746.9</v>
+      </c>
+      <c r="R135" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1734.0 above EMA200 Rs.1439.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1734.0</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 08:02 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 08:02 PM IST</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>2270.10009765625</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>1115754 / 661679 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="H136" s="4" t="n">
+        <v>2289.8</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>2158.7</v>
+      </c>
+      <c r="J136" s="6" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="K136" s="7" t="n">
+        <v>2552.1</v>
+      </c>
+      <c r="L136" s="8" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="M136" s="7" t="n">
+        <v>2683.2</v>
+      </c>
+      <c r="N136" s="8" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="O136" s="4" t="n">
+        <v>2120</v>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="n">
+        <v>2289.8</v>
+      </c>
+      <c r="R136" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2270.1 above EMA200 Rs.1940.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 65 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2270.1</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 08:02 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 08:02 PM IST</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>439.8999938964844</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>7669374 / 6316783 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="H137" s="4" t="n">
+        <v>443.6</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>419</v>
+      </c>
+      <c r="J137" s="6" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="K137" s="7" t="n">
+        <v>492.9</v>
+      </c>
+      <c r="L137" s="8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M137" s="7" t="n">
+        <v>517.5</v>
+      </c>
+      <c r="N137" s="8" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O137" s="4" t="n">
+        <v>429.2000122070312</v>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="n">
+        <v>443.6</v>
+      </c>
+      <c r="R137" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.439.9 above EMA200 Rs.358.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 439.9</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 08:02 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T137"/>
+  <dimension ref="A1:T138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10950,6 +10950,82 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>22/09/2026 08:26 PM IST</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>423.2000122070312</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>7366084 / 3474434 (2.1x)</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="n">
+        <v>424.4</v>
+      </c>
+      <c r="H138" s="4" t="n">
+        <v>427.7</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>405.8</v>
+      </c>
+      <c r="J138" s="6" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="K138" s="7" t="n">
+        <v>471.6</v>
+      </c>
+      <c r="L138" s="8" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="M138" s="7" t="n">
+        <v>493.5</v>
+      </c>
+      <c r="N138" s="8" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="O138" s="4" t="n">
+        <v>402.3999938964844</v>
+      </c>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="n">
+        <v>427.7</v>
+      </c>
+      <c r="R138" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.423.2 above EMA200 Rs.346.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.1x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.1x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 424.4</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>22/09/2026 08:26 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T138"/>
+  <dimension ref="A1:T141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11026,6 +11026,234 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>23/09/2026 08:32 PM IST</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>87.90000152587891</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>64505569 / 16466292 (3.9x)</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="H139" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="J139" s="6" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="K139" s="7" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="L139" s="8" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="M139" s="7" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="N139" s="8" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="O139" s="4" t="n">
+        <v>85.37000274658203</v>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="R139" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.87.9 above EMA200 Rs.78.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 3.9x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 3.9x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 89.6</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>23/09/2026 08:32 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>23/09/2026 08:32 PM IST</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>1042.5</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>2096025 / 739110 (2.8x)</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="n">
+        <v>1058</v>
+      </c>
+      <c r="H140" s="4" t="n">
+        <v>1066.4</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>1010.4</v>
+      </c>
+      <c r="J140" s="6" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="K140" s="7" t="n">
+        <v>1178.4</v>
+      </c>
+      <c r="L140" s="8" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="M140" s="7" t="n">
+        <v>1234.4</v>
+      </c>
+      <c r="N140" s="8" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="O140" s="4" t="n">
+        <v>1007</v>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="n">
+        <v>1066.4</v>
+      </c>
+      <c r="R140" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1042.5 above EMA200 Rs.897.9, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1058.0</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>23/09/2026 08:32 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>23/09/2026 08:32 PM IST</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>3374</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>2249338 / 1785408 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="n">
+        <v>3374</v>
+      </c>
+      <c r="H141" s="4" t="n">
+        <v>3404.3</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>3202.2</v>
+      </c>
+      <c r="J141" s="6" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="K141" s="7" t="n">
+        <v>3808.5</v>
+      </c>
+      <c r="L141" s="8" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="M141" s="7" t="n">
+        <v>4010.6</v>
+      </c>
+      <c r="N141" s="8" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="O141" s="4" t="n">
+        <v>3262.60009765625</v>
+      </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="n">
+        <v>3404.3</v>
+      </c>
+      <c r="R141" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.3374.0 above EMA200 Rs.2722.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 62 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 3374.0</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr">
+        <is>
+          <t>23/09/2026 08:32 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T141"/>
+  <dimension ref="A1:T142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11254,6 +11254,82 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>24/09/2026 08:38 PM IST</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>3427.699951171875</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>4132303 / 1781495 (2.3x)</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="n">
+        <v>3477</v>
+      </c>
+      <c r="H142" s="4" t="n">
+        <v>3507.4</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>3304.7</v>
+      </c>
+      <c r="J142" s="6" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="K142" s="7" t="n">
+        <v>3912.7</v>
+      </c>
+      <c r="L142" s="8" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="M142" s="7" t="n">
+        <v>4115.4</v>
+      </c>
+      <c r="N142" s="8" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="O142" s="4" t="n">
+        <v>3374</v>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="n">
+        <v>3507.4</v>
+      </c>
+      <c r="R142" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.3427.7 above EMA200 Rs.2728.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 3477.0</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr">
+        <is>
+          <t>24/09/2026 08:38 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T142"/>
+  <dimension ref="A1:T143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11330,6 +11330,82 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:47 PM IST</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>748.25</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>1774351 / 1206621 (1.5x)</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="n">
+        <v>766.8</v>
+      </c>
+      <c r="H143" s="4" t="n">
+        <v>774.2</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>732.3</v>
+      </c>
+      <c r="J143" s="6" t="n">
+        <v>-0.05400000000000001</v>
+      </c>
+      <c r="K143" s="7" t="n">
+        <v>858</v>
+      </c>
+      <c r="L143" s="8" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="M143" s="7" t="n">
+        <v>899.8</v>
+      </c>
+      <c r="N143" s="8" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="O143" s="4" t="n">
+        <v>738.9500122070312</v>
+      </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="n">
+        <v>774.2</v>
+      </c>
+      <c r="R143" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.748.2 above EMA200 Rs.732.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 53 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 766.8</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:47 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T143"/>
+  <dimension ref="A1:T145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11406,6 +11406,158 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026 10:01 PM IST</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>1822</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>4197624 / 1943400 (2.2x)</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="n">
+        <v>1822</v>
+      </c>
+      <c r="H144" s="4" t="n">
+        <v>1834</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>1754</v>
+      </c>
+      <c r="J144" s="6" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="K144" s="7" t="n">
+        <v>1994</v>
+      </c>
+      <c r="L144" s="8" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="M144" s="7" t="n">
+        <v>2074</v>
+      </c>
+      <c r="N144" s="8" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="O144" s="4" t="n">
+        <v>1743.699951171875</v>
+      </c>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="n">
+        <v>1834</v>
+      </c>
+      <c r="R144" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1822.0 above EMA200 Rs.1654.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 60 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1822.0</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026 10:01 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026 10:01 PM IST</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>2989.699951171875</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>876772 / 584873 (1.5x)</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="n">
+        <v>3024</v>
+      </c>
+      <c r="H145" s="4" t="n">
+        <v>3046.8</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>2894.5</v>
+      </c>
+      <c r="J145" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K145" s="7" t="n">
+        <v>3351.3</v>
+      </c>
+      <c r="L145" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M145" s="7" t="n">
+        <v>3503.6</v>
+      </c>
+      <c r="N145" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O145" s="4" t="n">
+        <v>2896</v>
+      </c>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="n">
+        <v>3046.8</v>
+      </c>
+      <c r="R145" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2989.7 above EMA200 Rs.2312.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.5x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.5x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 3024.0</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026 10:01 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T145"/>
+  <dimension ref="A1:T146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11558,6 +11558,82 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026 10:32 PM IST</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>411.3999938964844</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>5386481 / 4346309 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="H146" s="4" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>399.4</v>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="K146" s="7" t="n">
+        <v>464.7</v>
+      </c>
+      <c r="L146" s="8" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="M146" s="7" t="n">
+        <v>486.5</v>
+      </c>
+      <c r="N146" s="8" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="O146" s="4" t="n">
+        <v>403.3500061035156</v>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="R146" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.411.4 above EMA200 Rs.352.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 54 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 417.8</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026 10:32 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -11630,7 +11630,7 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026 10:32 PM IST</t>
+          <t>02/10/2026 09:46 PM IST</t>
         </is>
       </c>
     </row>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -11630,7 +11630,7 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026 09:46 PM IST</t>
+          <t>06/10/2026 12:48 AM IST</t>
         </is>
       </c>
     </row>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T146"/>
+  <dimension ref="A1:T150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11634,6 +11634,310 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026 10:19 PM IST</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>5098704 / 1645696 (3.1x)</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="n">
+        <v>297.9</v>
+      </c>
+      <c r="H147" s="4" t="n">
+        <v>299.7</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>287.1</v>
+      </c>
+      <c r="J147" s="6" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="K147" s="7" t="n">
+        <v>324.8</v>
+      </c>
+      <c r="L147" s="8" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="M147" s="7" t="n">
+        <v>337.4</v>
+      </c>
+      <c r="N147" s="8" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="O147" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="n">
+        <v>299.7</v>
+      </c>
+      <c r="R147" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.297.5 above EMA200 Rs.280.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 61 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 3.1x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 3.1x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 297.9</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026 10:19 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026 10:19 PM IST</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>BBOX</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>839.9500122070312</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>1120205 / 712644 (1.6x)</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="n">
+        <v>844.5</v>
+      </c>
+      <c r="H148" s="4" t="n">
+        <v>853</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>784.8</v>
+      </c>
+      <c r="J148" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K148" s="7" t="n">
+        <v>989.5</v>
+      </c>
+      <c r="L148" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M148" s="7" t="n">
+        <v>1057.7</v>
+      </c>
+      <c r="N148" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O148" s="4" t="n">
+        <v>812.5</v>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="R148" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.840.0 above EMA200 Rs.732.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 60 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 844.5</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026 10:19 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026 10:19 PM IST</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>1692.800048828125</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>1009591 / 751740 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="n">
+        <v>1696</v>
+      </c>
+      <c r="H149" s="4" t="n">
+        <v>1706.3</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>1641.1</v>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="K149" s="7" t="n">
+        <v>1836.8</v>
+      </c>
+      <c r="L149" s="8" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="M149" s="7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="N149" s="8" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="O149" s="4" t="n">
+        <v>1674.900024414062</v>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="n">
+        <v>1706.3</v>
+      </c>
+      <c r="R149" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1692.8 above EMA200 Rs.1473.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 54 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1696.0</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026 10:19 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026 10:19 PM IST</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>2196922 / 1572929 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="n">
+        <v>2054.9</v>
+      </c>
+      <c r="H150" s="4" t="n">
+        <v>2069</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>1975.3</v>
+      </c>
+      <c r="J150" s="6" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="K150" s="7" t="n">
+        <v>2256.4</v>
+      </c>
+      <c r="L150" s="8" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="M150" s="7" t="n">
+        <v>2350.1</v>
+      </c>
+      <c r="N150" s="8" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="O150" s="4" t="n">
+        <v>1971.400024414062</v>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="n">
+        <v>2069</v>
+      </c>
+      <c r="R150" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2050.0 above EMA200 Rs.1476.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 67 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2054.9</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026 10:19 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T150"/>
+  <dimension ref="A1:T153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11938,6 +11938,234 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:56 PM IST</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>BBOX</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>884.8499755859375</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>2262078 / 688687 (3.3x)</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="n">
+        <v>893.1</v>
+      </c>
+      <c r="H151" s="4" t="n">
+        <v>902</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K151" s="7" t="n">
+        <v>1046.3</v>
+      </c>
+      <c r="L151" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M151" s="7" t="n">
+        <v>1118.5</v>
+      </c>
+      <c r="N151" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O151" s="4" t="n">
+        <v>839.9500122070312</v>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="n">
+        <v>902</v>
+      </c>
+      <c r="R151" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.884.8 above EMA200 Rs.734.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 3.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 3.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 893.1</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:56 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:56 PM IST</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>1732</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>5015516 / 4018949 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="n">
+        <v>1774</v>
+      </c>
+      <c r="H152" s="4" t="n">
+        <v>1790.2</v>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>1682</v>
+      </c>
+      <c r="J152" s="6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="K152" s="7" t="n">
+        <v>2006.7</v>
+      </c>
+      <c r="L152" s="8" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M152" s="7" t="n">
+        <v>2114.9</v>
+      </c>
+      <c r="N152" s="8" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="O152" s="4" t="n">
+        <v>1694</v>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="n">
+        <v>1790.2</v>
+      </c>
+      <c r="R152" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1732.0 above EMA200 Rs.1355.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 55 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1774.0</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:56 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:56 PM IST</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>1561.800048828125</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>656193 / 513632 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="n">
+        <v>1590</v>
+      </c>
+      <c r="H153" s="4" t="n">
+        <v>1604</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>1511</v>
+      </c>
+      <c r="J153" s="6" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="K153" s="7" t="n">
+        <v>1790.1</v>
+      </c>
+      <c r="L153" s="8" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="M153" s="7" t="n">
+        <v>1883.1</v>
+      </c>
+      <c r="N153" s="8" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="O153" s="4" t="n">
+        <v>1558.099975585938</v>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="n">
+        <v>1604</v>
+      </c>
+      <c r="R153" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1561.8 above EMA200 Rs.1232.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 53 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1590.0</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:56 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T153"/>
+  <dimension ref="A1:T155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12166,6 +12166,158 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026 11:06 PM IST</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>1763</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>3449553 / 2433695 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>1776.3</v>
+      </c>
+      <c r="H154" s="4" t="n">
+        <v>1790.7</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>1694.6</v>
+      </c>
+      <c r="J154" s="6" t="n">
+        <v>-0.05400000000000001</v>
+      </c>
+      <c r="K154" s="7" t="n">
+        <v>1982.8</v>
+      </c>
+      <c r="L154" s="8" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="M154" s="7" t="n">
+        <v>2078.9</v>
+      </c>
+      <c r="N154" s="8" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="O154" s="4" t="n">
+        <v>1761</v>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="n">
+        <v>1790.7</v>
+      </c>
+      <c r="R154" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1763.0 above EMA200 Rs.1657.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 51 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1776.3</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026 11:06 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026 11:06 PM IST</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>ABDL</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>718.4500122070312</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>1642988 / 1254839 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="n">
+        <v>731</v>
+      </c>
+      <c r="H155" s="4" t="n">
+        <v>738.3</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>679.2</v>
+      </c>
+      <c r="J155" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K155" s="7" t="n">
+        <v>856.4</v>
+      </c>
+      <c r="L155" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M155" s="7" t="n">
+        <v>915.5</v>
+      </c>
+      <c r="N155" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O155" s="4" t="n">
+        <v>711.5499877929688</v>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="n">
+        <v>738.3</v>
+      </c>
+      <c r="R155" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.718.5 above EMA200 Rs.590.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 731.0</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026 11:06 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T155"/>
+  <dimension ref="A1:T158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12318,6 +12318,234 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026 08:40 PM IST</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>292.9500122070312</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>2676484 / 2048002 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="n">
+        <v>295</v>
+      </c>
+      <c r="H156" s="4" t="n">
+        <v>296.9</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>286.6</v>
+      </c>
+      <c r="J156" s="6" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="K156" s="7" t="n">
+        <v>317.6</v>
+      </c>
+      <c r="L156" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M156" s="7" t="n">
+        <v>327.9</v>
+      </c>
+      <c r="N156" s="8" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O156" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="n">
+        <v>296.9</v>
+      </c>
+      <c r="R156" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.293.0 above EMA200 Rs.281.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 55 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 295.0</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026 08:40 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026 08:40 PM IST</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>REDINGTON</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>401.6000061035156</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>5910473 / 4415034 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="n">
+        <v>411.5</v>
+      </c>
+      <c r="H157" s="4" t="n">
+        <v>415.6</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>386</v>
+      </c>
+      <c r="J157" s="6" t="n">
+        <v>-0.07099999999999999</v>
+      </c>
+      <c r="K157" s="7" t="n">
+        <v>474.7</v>
+      </c>
+      <c r="L157" s="8" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="M157" s="7" t="n">
+        <v>504.3</v>
+      </c>
+      <c r="N157" s="8" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="O157" s="4" t="n">
+        <v>391.9500122070312</v>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="n">
+        <v>415.6</v>
+      </c>
+      <c r="R157" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.401.6 above EMA200 Rs.303.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 56 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 411.5</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026 08:40 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026 08:40 PM IST</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>807</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>3221048 / 2587136 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="n">
+        <v>823.8</v>
+      </c>
+      <c r="H158" s="4" t="n">
+        <v>831</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>782.6</v>
+      </c>
+      <c r="J158" s="6" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="K158" s="7" t="n">
+        <v>927.7</v>
+      </c>
+      <c r="L158" s="8" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="M158" s="7" t="n">
+        <v>976.1</v>
+      </c>
+      <c r="N158" s="8" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="O158" s="4" t="n">
+        <v>802.9500122070312</v>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="R158" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.807.0 above EMA200 Rs.659.0, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 52 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: not yet confirmed bullish (daily setup still valid, extra caution advised); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 823.8</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026 08:40 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T158"/>
+  <dimension ref="A1:T159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12546,6 +12546,82 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>15/10/2026 08:33 PM IST</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>741.4500122070312</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>5010360 / 3457608 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="n">
+        <v>752.5</v>
+      </c>
+      <c r="H159" s="4" t="n">
+        <v>757.7</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>723.4</v>
+      </c>
+      <c r="J159" s="6" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="K159" s="7" t="n">
+        <v>826.3</v>
+      </c>
+      <c r="L159" s="8" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="M159" s="7" t="n">
+        <v>860.6</v>
+      </c>
+      <c r="N159" s="8" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="O159" s="4" t="n">
+        <v>725.4000244140625</v>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="n">
+        <v>757.7</v>
+      </c>
+      <c r="R159" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.741.5 above EMA200 Rs.706.6, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 752.5</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>15/10/2026 08:33 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T159"/>
+  <dimension ref="A1:T160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12622,6 +12622,82 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 08:22 PM IST</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>833.1500244140625</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>39118337 / 1877986 (20.8x)</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="n">
+        <v>842</v>
+      </c>
+      <c r="H160" s="4" t="n">
+        <v>850.4</v>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>782.4</v>
+      </c>
+      <c r="J160" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K160" s="7" t="n">
+        <v>986.5</v>
+      </c>
+      <c r="L160" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M160" s="7" t="n">
+        <v>1054.5</v>
+      </c>
+      <c r="N160" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O160" s="4" t="n">
+        <v>710.4500122070312</v>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="n">
+        <v>850.4</v>
+      </c>
+      <c r="R160" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.833.2 above EMA200 Rs.748.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 66 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 20.8x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 20.8x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 842.0</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026 08:22 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T160"/>
+  <dimension ref="A1:T161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12698,6 +12698,82 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026 10:29 PM IST</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>268.8099975585938</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>15112730 / 6986797 (2.2x)</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="n">
+        <v>268.8</v>
+      </c>
+      <c r="H161" s="4" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="I161" s="5" t="n">
+        <v>249.8</v>
+      </c>
+      <c r="J161" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K161" s="7" t="n">
+        <v>314.9</v>
+      </c>
+      <c r="L161" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M161" s="7" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="N161" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O161" s="4" t="n">
+        <v>256.010009765625</v>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="R161" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.268.8 above EMA200 Rs.172.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 62 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 268.8</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026 10:29 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -12770,7 +12770,7 @@
       </c>
       <c r="T161" s="2" t="inlineStr">
         <is>
-          <t>19/10/2026 10:29 PM IST</t>
+          <t>20/10/2026 08:37 PM IST</t>
         </is>
       </c>
     </row>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T161"/>
+  <dimension ref="A1:T162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12774,6 +12774,82 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 08:48 PM IST</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>1453.699951171875</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>4857684 / 2952626 (1.6x)</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H162" s="4" t="n">
+        <v>1494.8</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>1375.2</v>
+      </c>
+      <c r="J162" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K162" s="7" t="n">
+        <v>1734</v>
+      </c>
+      <c r="L162" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M162" s="7" t="n">
+        <v>1853.6</v>
+      </c>
+      <c r="N162" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O162" s="4" t="n">
+        <v>1438.400024414062</v>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="n">
+        <v>1494.8</v>
+      </c>
+      <c r="R162" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.1453.7 above EMA200 Rs.1158.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 51 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.6x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.6x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 1480.0</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>22/10/2026 08:48 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T162"/>
+  <dimension ref="A1:T165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12850,6 +12850,234 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026 10:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>389</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>8361344 / 4808563 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="n">
+        <v>389</v>
+      </c>
+      <c r="H163" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>372.2</v>
+      </c>
+      <c r="J163" s="6" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="K163" s="7" t="n">
+        <v>431.6</v>
+      </c>
+      <c r="L163" s="8" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="M163" s="7" t="n">
+        <v>451.4</v>
+      </c>
+      <c r="N163" s="8" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="O163" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="R163" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.389.0 above EMA200 Rs.387.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 389.0</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026 10:18 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026 10:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>2058.89990234375</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>1858038 / 1452991 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="n">
+        <v>2058.9</v>
+      </c>
+      <c r="H164" s="4" t="n">
+        <v>2077.2</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>1955.3</v>
+      </c>
+      <c r="J164" s="6" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="K164" s="7" t="n">
+        <v>2320.9</v>
+      </c>
+      <c r="L164" s="8" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="M164" s="7" t="n">
+        <v>2442.8</v>
+      </c>
+      <c r="N164" s="8" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="O164" s="4" t="n">
+        <v>1970</v>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="n">
+        <v>2077.2</v>
+      </c>
+      <c r="R164" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2058.9 above EMA200 Rs.1537.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 57 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2058.9</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026 10:18 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026 10:18 PM IST</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>440.75</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>32584687 / 26134929 (1.2x)</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="n">
+        <v>446.3</v>
+      </c>
+      <c r="H165" s="4" t="n">
+        <v>449.4</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>428.7</v>
+      </c>
+      <c r="J165" s="6" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="K165" s="7" t="n">
+        <v>490.7</v>
+      </c>
+      <c r="L165" s="8" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="M165" s="7" t="n">
+        <v>511.4</v>
+      </c>
+      <c r="N165" s="8" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="O165" s="4" t="n">
+        <v>430.5</v>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="n">
+        <v>449.4</v>
+      </c>
+      <c r="R165" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.440.8 above EMA200 Rs.404.8, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 59 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.2x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.2x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 446.3</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026 10:18 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T165"/>
+  <dimension ref="A1:T166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13078,6 +13078,82 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>27/10/2026 09:23 PM IST</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>3116290 / 1476506 (2.1x)</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="n">
+        <v>2143.1</v>
+      </c>
+      <c r="H166" s="4" t="n">
+        <v>2161.1</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>2041.1</v>
+      </c>
+      <c r="J166" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K166" s="7" t="n">
+        <v>2401.2</v>
+      </c>
+      <c r="L166" s="8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M166" s="7" t="n">
+        <v>2521.2</v>
+      </c>
+      <c r="N166" s="8" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O166" s="4" t="n">
+        <v>2058.89990234375</v>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="n">
+        <v>2161.1</v>
+      </c>
+      <c r="R166" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.2142.0 above EMA200 Rs.1543.3, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 65 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 2.1x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 2.1x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 2143.1</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>27/10/2026 09:23 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T166"/>
+  <dimension ref="A1:T169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13154,6 +13154,234 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>29/10/2026 10:26 PM IST</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>459</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>46297204 / 27590459 (1.7x)</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="n">
+        <v>460.2</v>
+      </c>
+      <c r="H167" s="4" t="n">
+        <v>463.1</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>443.4</v>
+      </c>
+      <c r="J167" s="6" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="K167" s="7" t="n">
+        <v>502.4</v>
+      </c>
+      <c r="L167" s="8" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="M167" s="7" t="n">
+        <v>522.1</v>
+      </c>
+      <c r="N167" s="8" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="O167" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="n">
+        <v>463.1</v>
+      </c>
+      <c r="R167" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.459.0 above EMA200 Rs.406.1, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 68 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.7x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.7x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 460.2</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>29/10/2026 10:26 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>29/10/2026 10:26 PM IST</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>20550703 / 15720433 (1.3x)</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="H168" s="4" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="J168" s="6" t="n">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="K168" s="7" t="n">
+        <v>210.3</v>
+      </c>
+      <c r="L168" s="8" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="M168" s="7" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="N168" s="8" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="O168" s="4" t="n">
+        <v>182.9799957275391</v>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="R168" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.186.5 above EMA200 Rs.169.5, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 63 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 187.5</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>29/10/2026 10:26 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>29/10/2026 10:26 PM IST</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>123.9000015258789</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>27688467 / 20170775 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="H169" s="4" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="J169" s="6" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="K169" s="7" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="L169" s="8" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="M169" s="7" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="N169" s="8" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="O169" s="4" t="n">
+        <v>120.3099975585938</v>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="R169" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.123.9 above EMA200 Rs.112.7, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 64 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 123.9</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>29/10/2026 10:26 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_tracker.xlsx
+++ b/master_tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T169"/>
+  <dimension ref="A1:T171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13382,6 +13382,158 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>30/10/2026 10:12 PM IST</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>219.0800018310547</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>27968042 / 3818006 (7.3x)</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="H170" s="4" t="n">
+        <v>229.3</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="J170" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K170" s="7" t="n">
+        <v>266</v>
+      </c>
+      <c r="L170" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M170" s="7" t="n">
+        <v>284.3</v>
+      </c>
+      <c r="N170" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O170" s="4" t="n">
+        <v>212.1699981689453</v>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="n">
+        <v>229.3</v>
+      </c>
+      <c r="R170" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.219.1 above EMA200 Rs.170.4, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 53 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 7.3x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 7.3x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 227.0</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>30/10/2026 10:12 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>30/10/2026 10:12 PM IST</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>6048</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>1107581 / 768925 (1.4x)</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="n">
+        <v>6048.5</v>
+      </c>
+      <c r="H171" s="4" t="n">
+        <v>6109</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>5697.1</v>
+      </c>
+      <c r="J171" s="6" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="K171" s="7" t="n">
+        <v>6932.9</v>
+      </c>
+      <c r="L171" s="8" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="M171" s="7" t="n">
+        <v>7344.8</v>
+      </c>
+      <c r="N171" s="8" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="O171" s="4" t="n">
+        <v>5880</v>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="n">
+        <v>6109</v>
+      </c>
+      <c r="R171" s="9" t="inlineStr">
+        <is>
+          <t>PILLAR 1 (Trend): Price Rs.6048.0 above EMA200 Rs.5398.2, and above a rising daily trendline; PILLAR 2 (Momentum): RSI 65 (40-70 range, rising), EMA44 sloping up, price above EMA44, volume 1.4x 20d avg; PILLAR 3 (Volume confirmation): Up day + volume 1.4x avg (&gt;= 1.2x conviction threshold); Weekly bias: bullish (bonus context, not a hard gate); Entry pivot: 3-day high (daily proxy for 1H entry-candle high) @ Rs. 6048.5</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>30/10/2026 10:12 PM IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
